--- a/Bug Reports/BugReport.xlsx
+++ b/Bug Reports/BugReport.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t>Bug ID</t>
   </si>
@@ -56,6 +56,9 @@
     <t>Password Reset fails for valid username</t>
   </si>
   <si>
+    <t>Password reset message should be displayed</t>
+  </si>
+  <si>
     <t>High</t>
   </si>
   <si>
@@ -70,12 +73,7 @@
 3. Click Reset</t>
   </si>
   <si>
-    <t>Password reset message 
-should be displayed</t>
-  </si>
-  <si>
-    <t>Appropriate error message 
-should be displayed</t>
+    <t>Appropriate error message should be displayed</t>
   </si>
   <si>
     <t>Page keeps loading and then displays 
@@ -89,6 +87,27 @@
   </si>
   <si>
     <t>Medium</t>
+  </si>
+  <si>
+    <t>BUG002</t>
+  </si>
+  <si>
+    <t>BUG003</t>
+  </si>
+  <si>
+    <t>User can access Dashboard using browser 
+Back button after logout</t>
+  </si>
+  <si>
+    <t>1. Login with valid credentials.
+2. Click Logout.
+3. Press the browser Back button.</t>
+  </si>
+  <si>
+    <t>Dashboard should not be accessible after logout. User should be redirected to the Login page or shown an access denied message.</t>
+  </si>
+  <si>
+    <t>Dashboard page is accessible after logout using the browser Back button.</t>
   </si>
 </sst>
 </file>
@@ -421,13 +440,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="38.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.08984375" customWidth="1"/>
     <col min="6" max="6" width="7.81640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.08984375" bestFit="1" customWidth="1"/>
@@ -470,27 +489,30 @@
         <v>9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>16</v>
@@ -502,11 +524,43 @@
         <v>19</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="G4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C7" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Bug Reports/BugReport.xlsx
+++ b/Bug Reports/BugReport.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="30">
   <si>
     <t>Bug ID</t>
   </si>
@@ -108,6 +108,27 @@
   </si>
   <si>
     <t>Dashboard page is accessible after logout using the browser Back button.</t>
+  </si>
+  <si>
+    <t>Submitted timesheet can be modified directly
+after submission</t>
+  </si>
+  <si>
+    <t>1. Submit the timesheet.
+2. Reopen the submitted
+timesheet.
+3. Try to edit the submitted
+entries.</t>
+  </si>
+  <si>
+    <t>User should not be able to modify the
+submitted timesheet directly. The 
+submitted timesheet should become
+read-only.</t>
+  </si>
+  <si>
+    <t>User is able to modify the submitted 
+timesheet directly after submission.</t>
   </si>
 </sst>
 </file>
@@ -556,6 +577,29 @@
         <v>13</v>
       </c>
     </row>
+    <row r="5" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="B5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C6" s="3"/>
     </row>

--- a/Bug Reports/BugReport.xlsx
+++ b/Bug Reports/BugReport.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
   <si>
     <t>Bug ID</t>
   </si>
@@ -129,6 +129,33 @@
   <si>
     <t>User is able to modify the submitted 
 timesheet directly after submission.</t>
+  </si>
+  <si>
+    <t>BUG004</t>
+  </si>
+  <si>
+    <t>BUG005</t>
+  </si>
+  <si>
+    <t>Partial username search does not display 
+matching usernames</t>
+  </si>
+  <si>
+    <t>1. Navigate to the User Search
+page.
+2. Enter a partial username 
+(e.g., enter "Adm" for 
+username "Admin22").
+3. Click the Search button.</t>
+  </si>
+  <si>
+    <t>Matching usernames containing the 
+entered partial text should be displayed.</t>
+  </si>
+  <si>
+    <t>Matching usrnames were not displayed 
+after performing the partial username
+search.</t>
   </si>
 </sst>
 </file>
@@ -469,7 +496,7 @@
     <col min="4" max="4" width="35.6328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="37.08984375" customWidth="1"/>
     <col min="6" max="6" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.08984375" customWidth="1"/>
     <col min="8" max="8" width="6.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -578,6 +605,9 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
       <c r="B5" s="2" t="s">
         <v>26</v>
       </c>
@@ -600,8 +630,31 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C6" s="3"/>
+    <row r="6" spans="1:8" ht="87" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C7" s="3"/>

--- a/Bug Reports/BugReport.xlsx
+++ b/Bug Reports/BugReport.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
   <si>
     <t>Bug ID</t>
   </si>
@@ -156,6 +156,29 @@
     <t>Matching usrnames were not displayed 
 after performing the partial username
 search.</t>
+  </si>
+  <si>
+    <t>BUG006</t>
+  </si>
+  <si>
+    <t>No message displayed when searching with 
+an invalid keyword</t>
+  </si>
+  <si>
+    <t>1. Enter an invalid keyword
+in the search field.
+2. Click the Search button.</t>
+  </si>
+  <si>
+    <t>A "No matching records found" message
+should be displayed.</t>
+  </si>
+  <si>
+    <t>No message was displayed when the invalid 
+keyword search returned no results</t>
+  </si>
+  <si>
+    <t>Low</t>
   </si>
 </sst>
 </file>
@@ -656,8 +679,31 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C7" s="3"/>
+    <row r="7" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Bug Reports/BugReport.xlsx
+++ b/Bug Reports/BugReport.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="47">
   <si>
     <t>Bug ID</t>
   </si>
@@ -179,6 +179,28 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>BUG007</t>
+  </si>
+  <si>
+    <t>Validation message is not displayed when 
+posting empty content</t>
+  </si>
+  <si>
+    <t>1. Navigate to the Buzz module.
+2. Leave the post content field
+empty.
+3. Click the Post button.</t>
+  </si>
+  <si>
+    <t>A validation message should be displayed 
+indicating that the post content cannot be 
+empty.</t>
+  </si>
+  <si>
+    <t>No validation message was displayed when
+the user attended post with empty content.</t>
   </si>
 </sst>
 </file>
@@ -511,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="38.7265625" bestFit="1" customWidth="1"/>
@@ -705,6 +727,32 @@
         <v>13</v>
       </c>
     </row>
+    <row r="8" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Bug Reports/BugReport.xlsx
+++ b/Bug Reports/BugReport.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="63">
   <si>
     <t>Bug ID</t>
   </si>
@@ -201,6 +201,85 @@
   <si>
     <t>No validation message was displayed when
 the user attended post with empty content.</t>
+  </si>
+  <si>
+    <t>BUG008</t>
+  </si>
+  <si>
+    <t>BUG009</t>
+  </si>
+  <si>
+    <t>BUG010</t>
+  </si>
+  <si>
+    <t>Account is not locked after multiple failed
+login attempts</t>
+  </si>
+  <si>
+    <t>1. Navigate to the login page.
+2. Enter a valid username.
+3. Enter an incorrect password
+multiple times (e.g., 10-15 
+consective attempts).
+4. Observe the system behavior.</t>
+  </si>
+  <si>
+    <t>The account should be temporarily locked
+or restricted after multiple failed login
+attempts, and an appropriate lockout
+message should be displayed.</t>
+  </si>
+  <si>
+    <t>The system continuosly displayed the 
+"Invalid credentials" message and does not
+lock or restrict the account after multiple
+failed attempts.</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>User can access Dashboard directly after
+logout</t>
+  </si>
+  <si>
+    <t>1. Login to the application.
+2. Logout from the application.
+3. Directly access a protected 
+URL (e.g., Dashboard URL).</t>
+  </si>
+  <si>
+    <t>User should be redirected to the login page
+when attempting to access a protected
+URL after logout.</t>
+  </si>
+  <si>
+    <t>User was redirected to the Dashboard and 
+cpuld access the appliaction even after
+logout.</t>
+  </si>
+  <si>
+    <t>Protected pages are accessible using browser
+Back button after logout.</t>
+  </si>
+  <si>
+    <t>1. Login to the application.
+2. Logout from the application.
+3. Click the browser Back 
+button.
+4. Observe whether protected
+pages are accessible.</t>
+  </si>
+  <si>
+    <t>Protected pages should not be accessible
+after logout. The user should be redirected
+to the Login page or shown access denined
+message.</t>
+  </si>
+  <si>
+    <t>Protected page remained accessible after
+logout when the browser Back button was
+used.</t>
   </si>
 </sst>
 </file>
@@ -533,7 +612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="38.7265625" bestFit="1" customWidth="1"/>
@@ -753,6 +832,84 @@
         <v>13</v>
       </c>
     </row>
+    <row r="9" spans="1:8" ht="116" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
